--- a/public/exports-from-60/29189447.xlsx
+++ b/public/exports-from-60/29189447.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042618</t>
+          <t xml:space="preserve">200042632</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -17914,12 +17914,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865121</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -17989,12 +17989,12 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865121</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911471</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23764,12 +23764,12 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911826</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -23839,12 +23839,12 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911826</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
